--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_974_Korea_North_Sea_of_Japan.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_974_Korea_North_Sea_of_Japan.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R055cb58994df4525"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6ee8b98ef4d14370"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb4de02f07f904dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4a7b0df1b7254b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rdcd428938af84329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3b08a867e0d049a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4392fc6b30374d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R998abeb226f2488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1f315027e5e74fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8ca3895795624e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbf5c309f8d81458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd42cb32cf1e54ac8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ974CommercialTable" displayName="EEZ974CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ974CommercialTable" displayName="EEZ974CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ974FunctionalTable" displayName="EEZ974FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ974FunctionalTable" displayName="EEZ974FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ974ValidationTable" displayName="EEZ974ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ974ValidationTable" displayName="EEZ974ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4245,7 +4199,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref53aa4c7f834b74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf50764c97cd493e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4255,20 +4209,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4276,660 +4220,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>7687.1356810937</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.14</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.03842646028852</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>7687.1356810937</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$54,A2,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1061120.1134049126</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.14</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1061120.1134049126</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>66944.3556028422</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.573675492278511</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>374.69292457858927</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>66944.3556028422</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>378.22527630172834</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$54,A3,'Species'!$U$2:$U$54))</x:f>
-        <x:v>25320047.39472615</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.573675492278511</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>374.69292457858927</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>25083576.384858012</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>236471.00986813754</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.009427324327279</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.009427324327279182</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>15404.1233262686</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.7755203461456595</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>59.63762586510031</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>15404.1233262686</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>81.74114704596339</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$54,A4,'Species'!$U$2:$U$54))</x:f>
-        <x:v>1259150.7099266762</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.7755203461456595</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>59.63762586510031</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>918665.3437118713</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>340485.36621480493</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3706304679341361</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.37063046793413623</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2082.3663918346997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5823860554452374</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>382.28394179576696</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2082.3663918346997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>398.7454479511605</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$54,A5,'Species'!$U$2:$U$54))</x:f>
-        <x:v>830334.1197105692</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5823860554452374</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>382.28394179576696</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>796055.2325335976</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>34278.88717697153</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0430609407187394</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04306094071873937</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>15840.1067242704</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9479427524406594</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>88.70390771668812</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>15840.1067242704</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>95.28576729390758</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$54,A6,'Species'!$U$2:$U$54))</x:f>
-        <x:v>1509336.72323949</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9479427524406594</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>88.70390771668812</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1405079.3650921725</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>104257.35814731754</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0742003339722226</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07420033397222249</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>762.0436812088999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0503483716734636</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.229188485686128</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>762.0436812088999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>11.303647286871735</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$54,A7,'Species'!$U$2:$U$54))</x:f>
-        <x:v>8613.872989574731</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0503483716734636</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.229188485686128</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8557.13213062085</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>56.74085895388089</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.006630826553541</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00663082655354115</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>56758.4051818914</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7377375620925593</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>546.6855088715962</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>56758.4051818914</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>935.1987364172506</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$54,A8,'Species'!$U$2:$U$54))</x:f>
-        <x:v>53080388.80716317</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7377375620925593</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>546.6855088715962</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>31028997.619602542</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>22051391.18756063</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7106704334409333</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7106704334409334</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8946.656581318899</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.3661339369661154</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>232.3453241786076</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8946.656581318899</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>513.4227798615786</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$54,A9,'Species'!$U$2:$U$54))</x:f>
-        <x:v>4593417.292447637</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.3661339369661154</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>232.3453241786076</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2078713.8237012129</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2514703.4687464237</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.20974009989933</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.2097400998993302</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>160.39991036409998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>398.1071705534973</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>160.39991036409998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$54,A10,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>63856.35447208644</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>63856.35447208644</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2499.0905431578003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.60317065565859</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>401.0242688262613</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2499.0905431578003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>401.7532214938647</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$54,A11,'Species'!$U$2:$U$54))</x:f>
-        <x:v>1004017.6765184985</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.60317065565859</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>401.0242688262613</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1002195.957800481</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1821.7187180174515</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0018177270660875</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0018177270660875312</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.0036988551</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.0036988551</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2238.721138568337</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$54,A12,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>8.280705100871302</x:v>
       </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>8.280705100871302</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd8417d99f044ca0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad500db5d3934b92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4939,20 +4454,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4960,984 +4465,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>27176.2271588024</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.20997509023265</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1621.7170780935708</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>27176.2271588024</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1695.1704829212135</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$54,A2,'Species'!$U$2:$U$54))</x:f>
-        <x:v>46068338.116763666</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.20997509023265</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1621.7170780935708</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>44072151.701580174</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1996186.415183492</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0452936001105642</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.04529360011056416</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1314.5146390063</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.7809339516957863</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>603.8567867411115</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1314.5146390063</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1896.8936917241404</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$54,A3,'Species'!$U$2:$U$54))</x:f>
-        <x:v>2493494.526410086</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.7809339516957863</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>603.8567867411115</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>793778.5860344964</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1699715.9403755898</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>3.1412972966011994</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>2.1412972966011994</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>725.4572956851</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.253529773387894</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1792.7914543317777</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>725.4572956851</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1850.76088487137</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$54,A4,'Species'!$U$2:$U$54))</x:f>
-        <x:v>1342647.9864985468</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.253529773387894</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1792.7914543317777</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1300593.6401868889</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>42054.34631165792</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0323347316273321</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.03233473162733205</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>41.7039766947</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.25</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1778.2794100389228</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>41.7039766947</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$54,A5,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>74161.3230729281</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.25</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>74161.3230729281</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>157.46683416850001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>157.46683416850001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$54,A6,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>352524.33027645596</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>352524.33027645596</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>160.92179213010002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5751554719927876</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>375.9719734641738</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>160.92179213010002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>394.0699776757115</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$54,A7,'Species'!$U$2:$U$54))</x:f>
-        <x:v>63414.447032244</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5751554719927876</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>375.9719734641738</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>60502.083760545254</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2912.3632716987486</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0481365779602778</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04813657796027787</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.0036988551</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.0036988551</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2238.721138568337</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$54,A8,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>8.280705100871302</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>8.280705100871302</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3050.9398347091997</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.046584319288439</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>111.32285077374624</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3050.9398347091997</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>174.7165685326999</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$54,A9,'Species'!$U$2:$U$54))</x:f>
-        <x:v>533049.738720114</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.046584319288439</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>111.32285077374624</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>339639.31993901025</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>193410.41878110374</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.569458267717162</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.569458267717162</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>67133.2771656204</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.568346066567301</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>370.12299396717134</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>67133.2771656204</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>370.48794429014424</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$54,A10,'Species'!$U$2:$U$54))</x:f>
-        <x:v>24872069.850551184</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.568346066567301</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>370.12299396717134</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>24847569.53936736</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>24500.311183825135</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0009860244538207</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0009860244538206426</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>30408.068033715703</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.319075342288478</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>208.48525361771226</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>30408.068033715703</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>215.7874819679416</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$54,A11,'Species'!$U$2:$U$54))</x:f>
-        <x:v>6561680.432505368</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.319075342288478</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>208.48525361771226</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6339633.776033867</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>222046.6564715011</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0350251551297678</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03502515512976769</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>19445.6730311308</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.078754611554844</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>119.88217441638855</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>19445.6730311308</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>168.1277440773961</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$54,A12,'Species'!$U$2:$U$54))</x:f>
-        <x:v>3269357.138790682</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.078754611554844</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>119.88217441638855</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2331189.5659620855</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>938167.5728285965</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.4024415631087528</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.40244156310875273</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1624.8361620023002</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.240690632662834</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>17.405665484601776</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1624.8361620023002</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>20.095223242536623</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$54,A13,'Species'!$U$2:$U$54))</x:f>
-        <x:v>32651.445407982625</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.240690632662834</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>17.405665484601776</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>28281.354703096258</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4370.090704886366</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1545219721885502</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.1545219721885503</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>12353.1834915594</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.708574050562749</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>51.11802317838805</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>12353.1834915594</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>58.778449433920244</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$54,A14,'Species'!$U$2:$U$54))</x:f>
-        <x:v>726100.9712065626</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.708574050562749</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>51.11802317838805</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>631470.320048414</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>94630.65115814854</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.149857638837077</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.1498576388370768</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>667.2636264531</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>667.2636264531</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$54,A15,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>215922.27702008394</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>215922.27702008394</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3013.9445329497</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3013.9445329497</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$54,A16,'Species'!$U$2:$U$54))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>301394.45329497</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>301394.45329497</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>7770.5436344830005</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.137101856900311</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>137.1203322502637</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>7770.5436344830005</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>137.3524531377614</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$54,A17,'Species'!$U$2:$U$54))</x:f>
-        <x:v>1067303.2304102564</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.137101856900311</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>137.1203322502637</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1065499.5249254806</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1803.7054847758263</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0016928261745608</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0016928261745606829</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>2040.66241514</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.568742369856576</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>370.4608935059097</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>2040.66241514</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>370.55261616398406</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$54,A18,'Species'!$U$2:$U$54))</x:f>
-        <x:v>756172.796637641</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.568742369856576</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>370.4608935059097</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>755985.621656692</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>187.1749809490284</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0002475906625563</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.00024759066255631543</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd85b433a056a451d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f0d02fb54b54210"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6112,7 +4978,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6211,7 +5077,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>88730291.34530385</x:v>
+        <x:v>63446825.60801261</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6225,7 +5091,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>88730291.34530388</x:v>
+        <x:v>83510305.69856766</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6239,7 +5105,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-25283465.73729124</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6253,7 +5119,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-5219985.64673619</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6264,9 +5130,9 @@
         <x:v>EEZ_974</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6278,47 +5144,19 @@
         <x:v>EEZ_974</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_974</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_974</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53bf079300a84324"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea302be25a0045b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6365,7 +5203,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
